--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateError.xlsx
@@ -61,7 +61,18 @@
     <t>区域</t>
   </si>
   <si>
-    <t>收货人</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>收货人</t>
+    </r>
   </si>
   <si>
     <t>邮编</t>
@@ -146,7 +157,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +167,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -638,137 +656,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -780,6 +798,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1177,7 +1198,7 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateError.xlsx
@@ -62,6 +62,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateError.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>销售单号</t>
   </si>
@@ -91,6 +91,9 @@
     <t>收件人税号</t>
   </si>
   <si>
+    <t>IE号</t>
+  </si>
+  <si>
     <t>收件人地址1</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
   </si>
   <si>
     <t>{.receiverTaxNo}</t>
+  </si>
+  <si>
+    <t>{.ieNo}</t>
   </si>
   <si>
     <t>{.firstAddress}</t>
@@ -1158,7 +1164,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1167,17 +1173,17 @@
     <col min="10" max="10" width="16.625" customWidth="1"/>
     <col min="11" max="11" width="12.625" customWidth="1"/>
     <col min="12" max="12" width="19.625" customWidth="1"/>
-    <col min="13" max="13" width="15.625" customWidth="1"/>
-    <col min="14" max="14" width="26.125" customWidth="1"/>
-    <col min="15" max="15" width="15.625" customWidth="1"/>
-    <col min="16" max="16" width="17.25" customWidth="1"/>
-    <col min="17" max="17" width="20.625" customWidth="1"/>
-    <col min="18" max="18" width="15.625" customWidth="1"/>
-    <col min="19" max="19" width="22" customWidth="1"/>
-    <col min="20" max="20" width="40" customWidth="1"/>
+    <col min="13" max="14" width="15.625" customWidth="1"/>
+    <col min="15" max="15" width="26.125" customWidth="1"/>
+    <col min="16" max="16" width="15.625" customWidth="1"/>
+    <col min="17" max="17" width="17.25" customWidth="1"/>
+    <col min="18" max="18" width="20.625" customWidth="1"/>
+    <col min="19" max="19" width="15.625" customWidth="1"/>
+    <col min="20" max="20" width="22" customWidth="1"/>
+    <col min="21" max="21" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1226,61 +1232,67 @@
       <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:17">
+    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
